--- a/Data/collapsed database manual cases/aguascalientes_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/aguascalientes_collapsed_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98420729-0D24-E64F-A465-462BDAE69BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ECD635-678A-4A46-8B6C-AD369095024D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="195">
   <si>
     <t>uniqueid</t>
   </si>
@@ -593,6 +593,21 @@
   </si>
   <si>
     <t>María Teresa Jiménez Esquivel</t>
+  </si>
+  <si>
+    <t>LEONARDO MONTA√ëEZ¬† CASTRO</t>
+  </si>
+  <si>
+    <t>DANIEL ROMO URRUTIA</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER RIVERA¬† LUEVANO</t>
+  </si>
+  <si>
+    <t>https://pan.org.mx/alcaldes/#AlcaldesNG</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://www.panags.org/images/Nuestros%2520candidatos/Curriculum/JOS%25C3%2589%2520ANTONIO%2520AR%25C3%2581MBULA%2520L%25C3%2593PEZ.pdf&amp;ved=2ahUKEwjyg73FsbeTAxWxEUQIHWFfKGwQFnoECBsQAQ&amp;usg=AOvVaw24UGjARxQ6i5Aq2cgeprl_</t>
   </si>
 </sst>
 </file>
@@ -964,7 +979,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -3727,6 +3742,83 @@
         <v>189</v>
       </c>
     </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>1001</v>
+      </c>
+      <c r="B58">
+        <v>2024</v>
+      </c>
+      <c r="E58" t="s">
+        <v>188</v>
+      </c>
+      <c r="F58" t="s">
+        <v>190</v>
+      </c>
+      <c r="H58" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>1003</v>
+      </c>
+      <c r="B59">
+        <v>2024</v>
+      </c>
+      <c r="E59" t="s">
+        <v>188</v>
+      </c>
+      <c r="F59" t="s">
+        <v>191</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>1005</v>
+      </c>
+      <c r="B60">
+        <v>2024</v>
+      </c>
+      <c r="E60" t="s">
+        <v>188</v>
+      </c>
+      <c r="F60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>1007</v>
+      </c>
+      <c r="B61">
+        <v>2024</v>
+      </c>
+      <c r="E61" t="s">
+        <v>188</v>
+      </c>
+      <c r="F61" t="s">
+        <v>192</v>
+      </c>
+      <c r="H61" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S56" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="6">
